--- a/grupos/1DV - Estadisticos 20221.xlsx
+++ b/grupos/1DV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="166">
   <si>
     <t>Materia</t>
   </si>
@@ -173,9 +173,6 @@
     <t>VAZQUEZ VELAZQUEZ ABRAHAM</t>
   </si>
   <si>
-    <t>VELASCO SAN JUAN DULCE REGINA</t>
-  </si>
-  <si>
     <t>ZEPAHUA TEZOCO MARISOL</t>
   </si>
   <si>
@@ -206,21 +203,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
-    <t>Villanueva Morales Luis Arturo</t>
+    <t>Medina Tolentino Francisco</t>
   </si>
   <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Francisco</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -239,31 +236,106 @@
     <t>ATLAHUA</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>ARCOS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>GERMAN</t>
+  </si>
+  <si>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAUL</t>
+  </si>
+  <si>
+    <t>JONATHAN YAEL</t>
+  </si>
+  <si>
+    <t>LUCIO ALEXIS</t>
+  </si>
+  <si>
+    <t>PABLO DIDIER</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>BRANDON</t>
+  </si>
+  <si>
+    <t>HECTOR MISAEL</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
+    <t>BAXIN</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
   </si>
   <si>
     <t>LOPEZ</t>
@@ -272,49 +344,73 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLMEDO</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>PANZO</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>UREÑA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
     <t>SOTO</t>
   </si>
   <si>
-    <t>FIERROS</t>
+    <t>CANO</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
   </si>
   <si>
     <t>FELIPE</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>ARCOS</t>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>------</t>
   </si>
   <si>
     <t>CASASOLA</t>
   </si>
   <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
     <t>VERA</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>GALLARDO</t>
   </si>
   <si>
     <t>CONTRERAS</t>
@@ -323,58 +419,58 @@
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
     <t>CHIPAHUA</t>
   </si>
   <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>JOSE</t>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
   </si>
   <si>
     <t>TEZOCO</t>
   </si>
   <si>
-    <t>GERMAN</t>
-  </si>
-  <si>
     <t>IGNACIO</t>
   </si>
   <si>
     <t>FERNANDA</t>
   </si>
   <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAUL</t>
+    <t>JARET ITZEL</t>
+  </si>
+  <si>
+    <t>LUIS JAVIER</t>
   </si>
   <si>
     <t>ELIDA CITLALI</t>
   </si>
   <si>
-    <t>JONATHAN YAEL</t>
-  </si>
-  <si>
-    <t>LUCIO ALEXIS</t>
-  </si>
-  <si>
-    <t>PABLO DIDIER</t>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>CARLOS DAVID</t>
   </si>
   <si>
     <t>SERGIO IVAN</t>
   </si>
   <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
+    <t>KATIA PAOLA</t>
+  </si>
+  <si>
+    <t>YAZMIN SINAI</t>
   </si>
   <si>
     <t>ZAID RAUL</t>
@@ -383,151 +479,43 @@
     <t>MARIA DE LOS ANGELES</t>
   </si>
   <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>SERGIO FARITH</t>
+  </si>
+  <si>
+    <t>AGUSTIN ARTURO</t>
+  </si>
+  <si>
     <t>ADAMARI</t>
   </si>
   <si>
+    <t>JULISSA</t>
+  </si>
+  <si>
     <t>ERIK</t>
   </si>
   <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
-  </si>
-  <si>
-    <t>HECTOR MISAEL</t>
+    <t>ROSA LIZBETH</t>
+  </si>
+  <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
+    <t>SAUL KOURCHENKOV</t>
+  </si>
+  <si>
+    <t>QUETZALY</t>
+  </si>
+  <si>
+    <t>ABRAHAM</t>
   </si>
   <si>
     <t>MARISOL</t>
-  </si>
-  <si>
-    <t>BAXIN</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLMEDO</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>UREÑA</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>CANO</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>------</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>JARET ITZEL</t>
-  </si>
-  <si>
-    <t>LUIS JAVIER</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>CARLOS DAVID</t>
-  </si>
-  <si>
-    <t>KATIA PAOLA</t>
-  </si>
-  <si>
-    <t>YAZMIN SINAI</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>SERGIO FARITH</t>
-  </si>
-  <si>
-    <t>AGUSTIN ARTURO</t>
-  </si>
-  <si>
-    <t>JULISSA</t>
-  </si>
-  <si>
-    <t>ROSA LIZBETH</t>
-  </si>
-  <si>
-    <t>OZIEL</t>
-  </si>
-  <si>
-    <t>SAUL KOURCHENKOV</t>
-  </si>
-  <si>
-    <t>QUETZALY</t>
-  </si>
-  <si>
-    <t>ABRAHAM</t>
-  </si>
-  <si>
-    <t>DULCE REGINA</t>
   </si>
 </sst>
 </file>
@@ -885,7 +873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y44"/>
+  <dimension ref="A1:Y43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1019,7 +1007,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>9</v>
@@ -1034,16 +1022,16 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1073,10 +1061,10 @@
         <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1096,7 +1084,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>9</v>
@@ -1111,16 +1099,16 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1150,13 +1138,13 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>9</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -1191,13 +1179,13 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1233,7 +1221,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>-1</v>
@@ -1250,7 +1238,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7">
         <v>10</v>
@@ -1265,16 +1253,16 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1301,16 +1289,16 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>10</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1330,7 +1318,7 @@
         <v>9</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F8">
         <v>6</v>
@@ -1345,13 +1333,13 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1381,10 +1369,10 @@
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>6</v>
@@ -1419,16 +1407,16 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1458,10 +1446,10 @@
         <v>6</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>7</v>
@@ -1481,7 +1469,7 @@
         <v>6</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -1496,16 +1484,16 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1535,13 +1523,13 @@
         <v>6</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>6</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>-1</v>
@@ -1558,10 +1546,10 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -1573,16 +1561,16 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1612,10 +1600,10 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>6</v>
@@ -1650,16 +1638,16 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1686,16 +1674,16 @@
         <v>6</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1718,7 +1706,7 @@
         <v>5</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -1730,13 +1718,13 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1766,13 +1754,13 @@
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>5</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>-1</v>
@@ -1804,16 +1792,16 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1840,16 +1828,16 @@
         <v>5</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>7</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -1881,16 +1869,16 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1923,10 +1911,10 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1943,7 +1931,7 @@
         <v>-1</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E16">
         <v>5</v>
@@ -1964,10 +1952,10 @@
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1997,13 +1985,13 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>5</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>-1</v>
@@ -2020,13 +2008,13 @@
         <v>-1</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G17">
         <v>-1</v>
@@ -2038,13 +2026,13 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2074,13 +2062,13 @@
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y17">
         <v>-1</v>
@@ -2097,7 +2085,7 @@
         <v>10</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E18">
         <v>9</v>
@@ -2112,16 +2100,16 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2148,10 +2136,10 @@
         <v>5</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2189,16 +2177,16 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2228,10 +2216,10 @@
         <v>7</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -2269,13 +2257,13 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2305,13 +2293,13 @@
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2328,10 +2316,10 @@
         <v>6</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F21">
         <v>8</v>
@@ -2343,10 +2331,10 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2382,10 +2370,10 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2420,16 +2408,16 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2456,13 +2444,13 @@
         <v>8</v>
       </c>
       <c r="U22">
+        <v>8</v>
+      </c>
+      <c r="V22">
+        <v>8</v>
+      </c>
+      <c r="W22">
         <v>10</v>
-      </c>
-      <c r="V22">
-        <v>7</v>
-      </c>
-      <c r="W22">
-        <v>9</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2482,7 +2470,7 @@
         <v>6</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E23">
         <v>8</v>
@@ -2497,16 +2485,16 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2533,16 +2521,16 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>8</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2559,7 +2547,7 @@
         <v>6</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E24">
         <v>7</v>
@@ -2574,16 +2562,16 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2613,13 +2601,13 @@
         <v>6</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -2651,16 +2639,16 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2690,10 +2678,10 @@
         <v>6</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>6</v>
@@ -2728,16 +2716,16 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2764,13 +2752,13 @@
         <v>5</v>
       </c>
       <c r="U26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>7</v>
@@ -2790,7 +2778,7 @@
         <v>6</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E27">
         <v>8</v>
@@ -2805,16 +2793,16 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2844,13 +2832,13 @@
         <v>6</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>6</v>
@@ -2867,7 +2855,7 @@
         <v>6</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E28">
         <v>6</v>
@@ -2882,16 +2870,16 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2921,10 +2909,10 @@
         <v>6</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>7</v>
@@ -2959,16 +2947,16 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -3001,10 +2989,10 @@
         <v>7</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -3036,16 +3024,16 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3081,7 +3069,7 @@
         <v>7</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>8</v>
@@ -3113,16 +3101,16 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3152,10 +3140,10 @@
         <v>6</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -3175,7 +3163,7 @@
         <v>6</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E32">
         <v>7</v>
@@ -3190,16 +3178,16 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3226,16 +3214,16 @@
         <v>7</v>
       </c>
       <c r="U32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>9</v>
@@ -3252,7 +3240,7 @@
         <v>6</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E33">
         <v>7</v>
@@ -3267,16 +3255,16 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3306,7 +3294,7 @@
         <v>6</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3332,7 +3320,7 @@
         <v>8</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F34">
         <v>8</v>
@@ -3344,16 +3332,16 @@
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3380,16 +3368,16 @@
         <v>5</v>
       </c>
       <c r="U34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34">
         <v>-1</v>
@@ -3421,16 +3409,16 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3457,10 +3445,10 @@
         <v>6</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W35">
         <v>10</v>
@@ -3483,10 +3471,10 @@
         <v>-1</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F36">
         <v>7</v>
@@ -3501,10 +3489,10 @@
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L36">
         <v>-1</v>
@@ -3537,10 +3525,10 @@
         <v>-1</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X36">
         <v>7</v>
@@ -3563,7 +3551,7 @@
         <v>6</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F37">
         <v>6</v>
@@ -3578,13 +3566,13 @@
         <v>-1</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -3614,13 +3602,13 @@
         <v>7</v>
       </c>
       <c r="V37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y37">
         <v>6</v>
@@ -3652,16 +3640,16 @@
         <v>-1</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M38">
         <v>-1</v>
@@ -3688,13 +3676,13 @@
         <v>6</v>
       </c>
       <c r="U38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X38">
         <v>7</v>
@@ -3729,16 +3717,16 @@
         <v>-1</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M39">
         <v>-1</v>
@@ -3774,7 +3762,7 @@
         <v>8</v>
       </c>
       <c r="X39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y39">
         <v>6</v>
@@ -3806,16 +3794,16 @@
         <v>-1</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M40">
         <v>-1</v>
@@ -3851,7 +3839,7 @@
         <v>9</v>
       </c>
       <c r="X40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y40">
         <v>6</v>
@@ -3883,16 +3871,16 @@
         <v>-1</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M41">
         <v>-1</v>
@@ -3922,13 +3910,13 @@
         <v>6</v>
       </c>
       <c r="V41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y41">
         <v>8</v>
@@ -3960,16 +3948,16 @@
         <v>-1</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M42">
         <v>-1</v>
@@ -4002,7 +3990,7 @@
         <v>7</v>
       </c>
       <c r="W42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X42">
         <v>7</v>
@@ -4016,16 +4004,16 @@
         <v>51</v>
       </c>
       <c r="B43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C43">
         <v>6</v>
       </c>
       <c r="D43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F43">
         <v>7</v>
@@ -4037,16 +4025,16 @@
         <v>-1</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M43">
         <v>-1</v>
@@ -4070,13 +4058,13 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U43">
         <v>6</v>
       </c>
       <c r="V43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W43">
         <v>9</v>
@@ -4085,83 +4073,6 @@
         <v>7</v>
       </c>
       <c r="Y43">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25">
-      <c r="A44" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B44">
-        <v>7</v>
-      </c>
-      <c r="C44">
-        <v>6</v>
-      </c>
-      <c r="D44">
-        <v>-1</v>
-      </c>
-      <c r="E44">
-        <v>8</v>
-      </c>
-      <c r="F44">
-        <v>7</v>
-      </c>
-      <c r="G44">
-        <v>6</v>
-      </c>
-      <c r="H44">
-        <v>-1</v>
-      </c>
-      <c r="I44">
-        <v>-1</v>
-      </c>
-      <c r="J44">
-        <v>-1</v>
-      </c>
-      <c r="K44">
-        <v>-1</v>
-      </c>
-      <c r="L44">
-        <v>-1</v>
-      </c>
-      <c r="M44">
-        <v>-1</v>
-      </c>
-      <c r="N44">
-        <v>-1</v>
-      </c>
-      <c r="O44">
-        <v>-1</v>
-      </c>
-      <c r="P44">
-        <v>-1</v>
-      </c>
-      <c r="Q44">
-        <v>-1</v>
-      </c>
-      <c r="R44">
-        <v>-1</v>
-      </c>
-      <c r="S44">
-        <v>-1</v>
-      </c>
-      <c r="T44">
-        <v>7</v>
-      </c>
-      <c r="U44">
-        <v>6</v>
-      </c>
-      <c r="V44">
-        <v>-1</v>
-      </c>
-      <c r="W44">
-        <v>8</v>
-      </c>
-      <c r="X44">
-        <v>7</v>
-      </c>
-      <c r="Y44">
         <v>6</v>
       </c>
     </row>
@@ -4189,191 +4100,191 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>60.98</v>
+        <v>67.5</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J2">
-        <v>39.02</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>65.84999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="G3">
-        <v>21.95</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>12.2</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4">
         <v>32</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>78.05</v>
+        <v>80</v>
       </c>
       <c r="G4">
-        <v>4.88</v>
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>17.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>78.05</v>
+        <v>82.5</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>21.95</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>80.48999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="G6">
-        <v>2.44</v>
+        <v>12.5</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>17.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4381,31 +4292,31 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>92.5</v>
+      </c>
+      <c r="G7">
+        <v>7.5</v>
+      </c>
+      <c r="H7">
+        <v>7.5</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>95.12</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>0</v>
-      </c>
-      <c r="H7">
-        <v>7.2</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>4.88</v>
       </c>
     </row>
   </sheetData>
@@ -4415,7 +4326,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4424,16 +4335,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -4447,19 +4358,19 @@
         <v>22330051920261</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4467,59 +4378,59 @@
         <v>22330051920261</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920396</v>
+        <v>22330051920263</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920260</v>
+        <v>22330051920263</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4527,96 +4438,96 @@
         <v>22330051920263</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920263</v>
+        <v>22330051920402</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920263</v>
+        <v>22330051920403</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" t="s">
         <v>92</v>
       </c>
-      <c r="D8" t="s">
-        <v>110</v>
-      </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920263</v>
+        <v>22330051920403</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" t="s">
         <v>92</v>
       </c>
-      <c r="D9" t="s">
-        <v>110</v>
-      </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920402</v>
+        <v>22330051920403</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>62</v>
@@ -4624,39 +4535,39 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920402</v>
+        <v>22330051920377</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920420</v>
+        <v>22330051920377</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" t="s">
         <v>93</v>
       </c>
-      <c r="D12" t="s">
-        <v>112</v>
-      </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>64</v>
@@ -4664,19 +4575,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920420</v>
+        <v>22330051920377</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" t="s">
         <v>93</v>
       </c>
-      <c r="D13" t="s">
-        <v>112</v>
-      </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>62</v>
@@ -4684,99 +4595,99 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920403</v>
+        <v>22330051920410</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" t="s">
         <v>94</v>
       </c>
-      <c r="D14" t="s">
-        <v>113</v>
-      </c>
       <c r="E14" t="s">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920403</v>
+        <v>22330051920410</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" t="s">
         <v>94</v>
       </c>
-      <c r="D15" t="s">
-        <v>113</v>
-      </c>
       <c r="E15" t="s">
         <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920403</v>
+        <v>22330051920410</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" t="s">
         <v>94</v>
-      </c>
-      <c r="D16" t="s">
-        <v>113</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920403</v>
+        <v>22330051920405</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920377</v>
+        <v>22330051920372</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
         <v>62</v>
@@ -4784,581 +4695,81 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>22330051920377</v>
+        <v>22330051920281</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="E19" t="s">
         <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>22330051920377</v>
+        <v>22330051920395</v>
       </c>
       <c r="B20" t="s">
         <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>22330051920377</v>
+        <v>22330051920395</v>
       </c>
       <c r="B21" t="s">
         <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>22330051920410</v>
+        <v>22330051920279</v>
       </c>
       <c r="B22" t="s">
         <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920410</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" t="s">
-        <v>115</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920410</v>
-      </c>
-      <c r="B24" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" t="s">
-        <v>74</v>
-      </c>
-      <c r="D24" t="s">
-        <v>115</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920410</v>
-      </c>
-      <c r="B25" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" t="s">
-        <v>115</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>22330051920410</v>
-      </c>
-      <c r="B26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" t="s">
-        <v>115</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>22330051920410</v>
-      </c>
-      <c r="B27" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" t="s">
-        <v>115</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>22330051920265</v>
-      </c>
-      <c r="B28" t="s">
-        <v>80</v>
-      </c>
-      <c r="C28" t="s">
-        <v>96</v>
-      </c>
-      <c r="D28" t="s">
-        <v>116</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>22330051920405</v>
-      </c>
-      <c r="B29" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" t="s">
-        <v>81</v>
-      </c>
-      <c r="D29" t="s">
-        <v>117</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>22330051920372</v>
-      </c>
-      <c r="B30" t="s">
-        <v>81</v>
-      </c>
-      <c r="C30" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>22330051920372</v>
-      </c>
-      <c r="B31" t="s">
-        <v>81</v>
-      </c>
-      <c r="C31" t="s">
-        <v>94</v>
-      </c>
-      <c r="D31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>22330051920372</v>
-      </c>
-      <c r="B32" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" t="s">
-        <v>94</v>
-      </c>
-      <c r="D32" t="s">
-        <v>118</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>22330051920268</v>
-      </c>
-      <c r="B33" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" t="s">
-        <v>97</v>
-      </c>
-      <c r="D33" t="s">
-        <v>119</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>22330051920270</v>
-      </c>
-      <c r="B34" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" t="s">
-        <v>98</v>
-      </c>
-      <c r="D34" t="s">
-        <v>120</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>22330051920273</v>
-      </c>
-      <c r="B35" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" t="s">
-        <v>99</v>
-      </c>
-      <c r="D35" t="s">
-        <v>105</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>22330051920375</v>
-      </c>
-      <c r="B36" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" t="s">
-        <v>100</v>
-      </c>
-      <c r="D36" t="s">
-        <v>121</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>22330051920276</v>
-      </c>
-      <c r="B37" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" t="s">
-        <v>101</v>
-      </c>
-      <c r="D37" t="s">
-        <v>122</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>22330051920281</v>
-      </c>
-      <c r="B38" t="s">
-        <v>86</v>
-      </c>
-      <c r="C38" t="s">
-        <v>102</v>
-      </c>
-      <c r="D38" t="s">
-        <v>123</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>22330051920281</v>
-      </c>
-      <c r="B39" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" t="s">
-        <v>102</v>
-      </c>
-      <c r="D39" t="s">
-        <v>123</v>
-      </c>
-      <c r="E39" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>22330051920277</v>
-      </c>
-      <c r="B40" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" t="s">
-        <v>103</v>
-      </c>
-      <c r="D40" t="s">
-        <v>118</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>22330051920395</v>
-      </c>
-      <c r="B41" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" t="s">
-        <v>104</v>
-      </c>
-      <c r="D41" t="s">
-        <v>124</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>22330051920395</v>
-      </c>
-      <c r="B42" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" t="s">
-        <v>104</v>
-      </c>
-      <c r="D42" t="s">
-        <v>124</v>
-      </c>
-      <c r="E42" t="s">
-        <v>7</v>
-      </c>
-      <c r="F42" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>22330051920395</v>
-      </c>
-      <c r="B43" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" t="s">
-        <v>104</v>
-      </c>
-      <c r="D43" t="s">
-        <v>124</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>22330051920395</v>
-      </c>
-      <c r="B44" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" t="s">
-        <v>104</v>
-      </c>
-      <c r="D44" t="s">
-        <v>124</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>22330051920279</v>
-      </c>
-      <c r="B45" t="s">
-        <v>87</v>
-      </c>
-      <c r="C45" t="s">
-        <v>105</v>
-      </c>
-      <c r="D45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>22330051920279</v>
-      </c>
-      <c r="B46" t="s">
-        <v>87</v>
-      </c>
-      <c r="C46" t="s">
-        <v>105</v>
-      </c>
-      <c r="D46" t="s">
-        <v>125</v>
-      </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>22330051920288</v>
-      </c>
-      <c r="B47" t="s">
-        <v>89</v>
-      </c>
-      <c r="C47" t="s">
-        <v>106</v>
-      </c>
-      <c r="D47" t="s">
-        <v>126</v>
-      </c>
-      <c r="E47" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" t="s">
         <v>62</v>
       </c>
     </row>
@@ -5369,7 +4780,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5378,172 +4789,172 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920410</v>
+        <v>22330051920263</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920263</v>
+        <v>22330051920403</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" t="s">
         <v>92</v>
       </c>
-      <c r="D3" t="s">
-        <v>110</v>
-      </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920403</v>
+        <v>22330051920377</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920377</v>
+        <v>22330051920410</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920395</v>
+        <v>22330051920261</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920372</v>
+        <v>22330051920395</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920261</v>
+        <v>22330051920402</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920402</v>
+        <v>22330051920405</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920420</v>
+        <v>22330051920372</v>
       </c>
       <c r="B10" t="s">
         <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5551,16 +4962,16 @@
         <v>22330051920281</v>
       </c>
       <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" t="s">
         <v>86</v>
       </c>
-      <c r="C11" t="s">
-        <v>102</v>
-      </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5568,16 +4979,16 @@
         <v>22330051920279</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5585,16 +4996,16 @@
         <v>21330051920396</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5602,183 +5013,183 @@
         <v>22330051920260</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920265</v>
+        <v>22330051920416</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920405</v>
+        <v>22330051920262</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920268</v>
+        <v>22330051920420</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920270</v>
+        <v>22330051920264</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920273</v>
+        <v>22330051920404</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920375</v>
+        <v>22330051920409</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920276</v>
+        <v>22330051920265</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920277</v>
+        <v>22330051920411</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920288</v>
+        <v>22330051920266</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920416</v>
+        <v>22330051920268</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="C24" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -5786,16 +5197,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920262</v>
+        <v>22330051920270</v>
       </c>
       <c r="B25" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -5803,16 +5214,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920264</v>
+        <v>22330051920271</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -5820,16 +5231,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920404</v>
+        <v>22330051920272</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="D27" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -5837,16 +5248,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920409</v>
+        <v>22330051920367</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5854,16 +5265,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920411</v>
+        <v>22330051920274</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5871,16 +5282,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920266</v>
+        <v>22330051920273</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="D30" t="s">
-        <v>158</v>
+        <v>88</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -5888,16 +5299,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920271</v>
+        <v>22330051920375</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="D31" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -5905,16 +5316,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330051920272</v>
+        <v>22330051920406</v>
       </c>
       <c r="B32" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="C32" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -5922,16 +5333,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>22330051920367</v>
+        <v>22330051920276</v>
       </c>
       <c r="B33" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -5939,16 +5350,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>22330051920274</v>
+        <v>22330051920277</v>
       </c>
       <c r="B34" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" t="s">
         <v>133</v>
       </c>
-      <c r="C34" t="s">
-        <v>136</v>
-      </c>
       <c r="D34" t="s">
-        <v>162</v>
+        <v>96</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -5956,16 +5367,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>22330051920406</v>
+        <v>22330051920280</v>
       </c>
       <c r="B35" t="s">
+        <v>115</v>
+      </c>
+      <c r="C35" t="s">
         <v>134</v>
       </c>
-      <c r="C35" t="s">
-        <v>88</v>
-      </c>
       <c r="D35" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -5973,16 +5384,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>22330051920280</v>
+        <v>22330051920407</v>
       </c>
       <c r="B36" t="s">
+        <v>116</v>
+      </c>
+      <c r="C36" t="s">
         <v>135</v>
       </c>
-      <c r="C36" t="s">
-        <v>146</v>
-      </c>
       <c r="D36" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -5990,16 +5401,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>22330051920407</v>
+        <v>22330051920282</v>
       </c>
       <c r="B37" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" t="s">
         <v>136</v>
       </c>
-      <c r="C37" t="s">
-        <v>147</v>
-      </c>
       <c r="D37" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -6007,16 +5418,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>22330051920282</v>
+        <v>22330051920283</v>
       </c>
       <c r="B38" t="s">
+        <v>118</v>
+      </c>
+      <c r="C38" t="s">
         <v>137</v>
       </c>
-      <c r="C38" t="s">
-        <v>148</v>
-      </c>
       <c r="D38" t="s">
-        <v>166</v>
+        <v>89</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -6024,16 +5435,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>22330051920283</v>
+        <v>22330051920285</v>
       </c>
       <c r="B39" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="C39" t="s">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="D39" t="s">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -6041,16 +5452,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>22330051920285</v>
+        <v>22330051920286</v>
       </c>
       <c r="B40" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C40" t="s">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="D40" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -6058,35 +5469,18 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>22330051920286</v>
+        <v>22330051920288</v>
       </c>
       <c r="B41" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="C41" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D41" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42">
-        <v>22330051920287</v>
-      </c>
-      <c r="B42" t="s">
-        <v>139</v>
-      </c>
-      <c r="C42" t="s">
-        <v>151</v>
-      </c>
-      <c r="D42" t="s">
-        <v>169</v>
-      </c>
-      <c r="E42">
         <v>0</v>
       </c>
     </row>
@@ -6097,7 +5491,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6106,22 +5500,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -6132,19 +5526,19 @@
         <v>22330051920261</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -6155,19 +5549,19 @@
         <v>22330051920261</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -6175,19 +5569,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920396</v>
+        <v>22330051920402</v>
       </c>
       <c r="B4" t="s">
         <v>73</v>
       </c>
       <c r="C4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" t="s">
         <v>91</v>
       </c>
-      <c r="D4" t="s">
-        <v>108</v>
-      </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>63</v>
@@ -6198,19 +5592,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920396</v>
+        <v>22330051920402</v>
       </c>
       <c r="B5" t="s">
         <v>73</v>
       </c>
       <c r="C5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" t="s">
         <v>91</v>
       </c>
-      <c r="D5" t="s">
-        <v>108</v>
-      </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>62</v>
@@ -6221,45 +5615,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920402</v>
+        <v>22330051920279</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920402</v>
+        <v>22330051920279</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -6267,48 +5661,48 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920420</v>
+        <v>21330051920396</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920420</v>
+        <v>22330051920404</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -6316,19 +5710,19 @@
         <v>22330051920265</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6336,22 +5730,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920265</v>
+        <v>22330051920405</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -6359,19 +5753,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920272</v>
+        <v>22330051920270</v>
       </c>
       <c r="B12" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>63</v>
@@ -6385,19 +5779,19 @@
         <v>22330051920272</v>
       </c>
       <c r="B13" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D13" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -6405,324 +5799,48 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920281</v>
+        <v>22330051920274</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="D14" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920281</v>
+        <v>22330051920288</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920260</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" t="s">
-        <v>109</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920404</v>
-      </c>
-      <c r="B17" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" t="s">
-        <v>142</v>
-      </c>
-      <c r="D17" t="s">
-        <v>155</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>63</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920405</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920268</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" t="s">
-        <v>119</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920270</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" t="s">
-        <v>120</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920274</v>
-      </c>
-      <c r="B21" t="s">
-        <v>133</v>
-      </c>
-      <c r="C21" t="s">
-        <v>136</v>
-      </c>
-      <c r="D21" t="s">
-        <v>162</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>63</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920273</v>
-      </c>
-      <c r="B22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" t="s">
-        <v>99</v>
-      </c>
-      <c r="D22" t="s">
-        <v>105</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920375</v>
-      </c>
-      <c r="B23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" t="s">
-        <v>100</v>
-      </c>
-      <c r="D23" t="s">
-        <v>121</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>62</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920276</v>
-      </c>
-      <c r="B24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" t="s">
-        <v>122</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920277</v>
-      </c>
-      <c r="B25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920287</v>
-      </c>
-      <c r="B26" t="s">
-        <v>139</v>
-      </c>
-      <c r="C26" t="s">
-        <v>151</v>
-      </c>
-      <c r="D26" t="s">
-        <v>169</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>63</v>
-      </c>
-      <c r="G26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920288</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>106</v>
-      </c>
-      <c r="D27" t="s">
-        <v>126</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>62</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1DV - Estadisticos 20221.xlsx
+++ b/grupos/1DV - Estadisticos 20221.xlsx
@@ -1105,7 +1105,7 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>8</v>
@@ -1141,7 +1141,7 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1182,7 +1182,7 @@
         <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -1218,7 +1218,7 @@
         <v>6</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -1721,7 +1721,7 @@
         <v>4</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>7</v>
@@ -2029,7 +2029,7 @@
         <v>4</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -2065,7 +2065,7 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -2337,7 +2337,7 @@
         <v>4</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2491,7 +2491,7 @@
         <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -3261,7 +3261,7 @@
         <v>6</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
         <v>7</v>
@@ -3569,7 +3569,7 @@
         <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L37">
         <v>5</v>
@@ -4266,19 +4266,19 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>87.5</v>
+        <v>85</v>
       </c>
       <c r="G6">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/1DV - Estadisticos 20221.xlsx
+++ b/grupos/1DV - Estadisticos 20221.xlsx
@@ -1034,7 +1034,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1111,7 +1111,7 @@
         <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -3563,7 +3563,7 @@
         <v>-1</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J37">
         <v>7</v>
@@ -3599,7 +3599,7 @@
         <v>-1</v>
       </c>
       <c r="U37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V37">
         <v>7</v>

--- a/grupos/1DV - Estadisticos 20221.xlsx
+++ b/grupos/1DV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="166">
   <si>
     <t>Materia</t>
   </si>
@@ -1265,7 +1265,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1301,7 +1301,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1419,7 +1419,7 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1455,7 +1455,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1487,7 +1487,7 @@
         <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>6</v>
@@ -1573,7 +1573,7 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1650,7 +1650,7 @@
         <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1804,7 +1804,7 @@
         <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1840,7 +1840,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1881,7 +1881,7 @@
         <v>8</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1949,7 +1949,7 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>5</v>
@@ -2112,7 +2112,7 @@
         <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2148,7 +2148,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2189,7 +2189,7 @@
         <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2266,7 +2266,7 @@
         <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2302,7 +2302,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2340,7 +2340,7 @@
         <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2376,7 +2376,7 @@
         <v>5</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>-1</v>
@@ -2420,7 +2420,7 @@
         <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2456,7 +2456,7 @@
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2497,7 +2497,7 @@
         <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2574,7 +2574,7 @@
         <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2651,7 +2651,7 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2687,7 +2687,7 @@
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2728,7 +2728,7 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2805,7 +2805,7 @@
         <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2841,7 +2841,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2882,7 +2882,7 @@
         <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2918,7 +2918,7 @@
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2959,7 +2959,7 @@
         <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2995,7 +2995,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3036,7 +3036,7 @@
         <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3113,7 +3113,7 @@
         <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3149,7 +3149,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3190,7 +3190,7 @@
         <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3226,7 +3226,7 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3267,7 +3267,7 @@
         <v>7</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3421,7 +3421,7 @@
         <v>6</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3495,7 +3495,7 @@
         <v>5</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3575,7 +3575,7 @@
         <v>5</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3652,7 +3652,7 @@
         <v>7</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3688,7 +3688,7 @@
         <v>7</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3729,7 +3729,7 @@
         <v>6</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3765,7 +3765,7 @@
         <v>8</v>
       </c>
       <c r="Y39">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3806,7 +3806,7 @@
         <v>9</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3883,7 +3883,7 @@
         <v>8</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3919,7 +3919,7 @@
         <v>7</v>
       </c>
       <c r="Y41">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3960,7 +3960,7 @@
         <v>6</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -4037,7 +4037,7 @@
         <v>7</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -4073,7 +4073,7 @@
         <v>7</v>
       </c>
       <c r="Y43">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4170,19 +4170,19 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>77.5</v>
+        <v>75</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
         <v>9</v>
@@ -5491,7 +5491,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5615,16 +5615,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920279</v>
+        <v>22330051920404</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -5638,16 +5638,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920279</v>
+        <v>22330051920404</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5656,21 +5656,21 @@
         <v>62</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920396</v>
+        <v>22330051920279</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -5684,39 +5684,39 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920404</v>
+        <v>22330051920279</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920265</v>
+        <v>21330051920396</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -5730,68 +5730,68 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920405</v>
+        <v>22330051920265</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920270</v>
+        <v>22330051920405</v>
       </c>
       <c r="B12" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
-        <v>152</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920272</v>
+        <v>22330051920270</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5799,16 +5799,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920274</v>
+        <v>22330051920272</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -5822,24 +5822,47 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
+        <v>22330051920274</v>
+      </c>
+      <c r="B15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D15" t="s">
+        <v>156</v>
+      </c>
+      <c r="E15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
         <v>22330051920288</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>120</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C16" t="s">
         <v>139</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>165</v>
       </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
         <v>63</v>
       </c>
-      <c r="G15">
+      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DV - Estadisticos 20221.xlsx
+++ b/grupos/1DV - Estadisticos 20221.xlsx
@@ -1019,7 +1019,7 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>6</v>
@@ -1096,7 +1096,7 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>6</v>
@@ -1173,7 +1173,7 @@
         <v>-1</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1209,7 +1209,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1250,7 +1250,7 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>10</v>
@@ -1286,7 +1286,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>8</v>
@@ -1404,7 +1404,7 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -1481,7 +1481,7 @@
         <v>-1</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>6</v>
@@ -1517,7 +1517,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>6</v>
@@ -1558,7 +1558,7 @@
         <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
         <v>6</v>
@@ -1594,7 +1594,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -1635,7 +1635,7 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>7</v>
@@ -1789,7 +1789,7 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>6</v>
@@ -1825,7 +1825,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>7</v>
@@ -1866,7 +1866,7 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>6</v>
@@ -1902,7 +1902,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>6</v>
@@ -2097,7 +2097,7 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>6</v>
@@ -2174,7 +2174,7 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I19">
         <v>6</v>
@@ -2210,7 +2210,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2251,7 +2251,7 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2328,7 +2328,7 @@
         <v>-1</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>6</v>
@@ -2405,7 +2405,7 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
         <v>6</v>
@@ -2441,7 +2441,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2482,7 +2482,7 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
         <v>7</v>
@@ -2518,7 +2518,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>7</v>
@@ -2559,7 +2559,7 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
         <v>6</v>
@@ -2636,7 +2636,7 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
         <v>6</v>
@@ -2713,7 +2713,7 @@
         <v>7</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I26">
         <v>7</v>
@@ -2790,7 +2790,7 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <v>6</v>
@@ -2867,7 +2867,7 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
         <v>6</v>
@@ -2944,7 +2944,7 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
         <v>6</v>
@@ -2980,7 +2980,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>7</v>
@@ -3021,7 +3021,7 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I30">
         <v>6</v>
@@ -3098,7 +3098,7 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I31">
         <v>6</v>
@@ -3134,7 +3134,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U31">
         <v>6</v>
@@ -3175,7 +3175,7 @@
         <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I32">
         <v>7</v>
@@ -3211,7 +3211,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U32">
         <v>7</v>
@@ -3252,7 +3252,7 @@
         <v>6</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>6</v>
@@ -3329,7 +3329,7 @@
         <v>-1</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>6</v>
@@ -3406,7 +3406,7 @@
         <v>7</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I35">
         <v>6</v>
@@ -3483,7 +3483,7 @@
         <v>-1</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I36">
         <v>-1</v>
@@ -3637,7 +3637,7 @@
         <v>8</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I38">
         <v>5</v>
@@ -3714,7 +3714,7 @@
         <v>6</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I39">
         <v>6</v>
@@ -3791,7 +3791,7 @@
         <v>6</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I40">
         <v>6</v>
@@ -3827,7 +3827,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U40">
         <v>6</v>
@@ -3868,7 +3868,7 @@
         <v>8</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I41">
         <v>6</v>
@@ -3945,7 +3945,7 @@
         <v>8</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I42">
         <v>6</v>
@@ -3981,7 +3981,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U42">
         <v>7</v>
@@ -4022,7 +4022,7 @@
         <v>6</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I43">
         <v>6</v>
@@ -4138,19 +4138,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>67.5</v>
+        <v>60</v>
       </c>
       <c r="G2">
-        <v>20</v>
+        <v>27.5</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
         <v>5</v>
@@ -5523,39 +5523,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920261</v>
+        <v>22330051920402</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920261</v>
+        <v>22330051920402</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5569,22 +5569,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920402</v>
+        <v>22330051920279</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5592,16 +5592,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920402</v>
+        <v>22330051920279</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5615,16 +5615,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920404</v>
+        <v>21330051920396</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -5661,16 +5661,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920279</v>
+        <v>22330051920265</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -5684,68 +5684,68 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920279</v>
+        <v>22330051920411</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>149</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920396</v>
+        <v>22330051920405</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920265</v>
+        <v>22330051920270</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5753,45 +5753,45 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920405</v>
+        <v>22330051920272</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920270</v>
+        <v>22330051920274</v>
       </c>
       <c r="B13" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5799,16 +5799,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920272</v>
+        <v>22330051920406</v>
       </c>
       <c r="B14" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C14" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -5822,16 +5822,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920274</v>
+        <v>22330051920283</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D15" t="s">
-        <v>156</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>

--- a/grupos/1DV - Estadisticos 20221.xlsx
+++ b/grupos/1DV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="166">
   <si>
     <t>Materia</t>
   </si>
@@ -206,12 +206,12 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>Medina Tolentino Francisco</t>
   </si>
   <si>
@@ -236,15 +236,33 @@
     <t>ATLAHUA</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BAXIN</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>ENCARNACION</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -254,253 +272,235 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLMEDO</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>ROSAS</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>UREÑA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
   </si>
   <si>
     <t>TEMOXTLE</t>
   </si>
   <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>CANO</t>
+  </si>
+  <si>
     <t>FIERROS</t>
   </si>
   <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>FELIPE</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
     <t>ARCOS</t>
   </si>
   <si>
-    <t>ANTONIO</t>
+    <t>------</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
   </si>
   <si>
     <t>ALVAREZ</t>
   </si>
   <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
     <t>GALINDO</t>
   </si>
   <si>
     <t>JOSE</t>
   </si>
   <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
     <t>GERMAN</t>
   </si>
   <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>FERNANDA</t>
+  </si>
+  <si>
+    <t>JARET ITZEL</t>
+  </si>
+  <si>
     <t>MIA</t>
   </si>
   <si>
+    <t>LUIS JAVIER</t>
+  </si>
+  <si>
     <t>GUILLERMO SAUL</t>
   </si>
   <si>
+    <t>ELIDA CITLALI</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
     <t>JONATHAN YAEL</t>
   </si>
   <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
     <t>LUCIO ALEXIS</t>
   </si>
   <si>
+    <t>CARLOS DAVID</t>
+  </si>
+  <si>
     <t>PABLO DIDIER</t>
   </si>
   <si>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>KATIA PAOLA</t>
+  </si>
+  <si>
     <t>JONATAN GILBERTO</t>
   </si>
   <si>
     <t>OSCAR</t>
   </si>
   <si>
+    <t>YAZMIN SINAI</t>
+  </si>
+  <si>
+    <t>ZAID RAUL</t>
+  </si>
+  <si>
+    <t>MARIA DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>SERGIO FARITH</t>
+  </si>
+  <si>
+    <t>AGUSTIN ARTURO</t>
+  </si>
+  <si>
+    <t>ADAMARI</t>
+  </si>
+  <si>
+    <t>JULISSA</t>
+  </si>
+  <si>
+    <t>ERIK</t>
+  </si>
+  <si>
     <t>MONSERRAT</t>
   </si>
   <si>
+    <t>ROSA LIZBETH</t>
+  </si>
+  <si>
     <t>BRANDON</t>
   </si>
   <si>
     <t>HECTOR MISAEL</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>BAXIN</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLMEDO</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>UREÑA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>CANO</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>FELIPE</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>------</t>
-  </si>
-  <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>FERNANDA</t>
-  </si>
-  <si>
-    <t>JARET ITZEL</t>
-  </si>
-  <si>
-    <t>LUIS JAVIER</t>
-  </si>
-  <si>
-    <t>ELIDA CITLALI</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>CARLOS DAVID</t>
-  </si>
-  <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
-    <t>KATIA PAOLA</t>
-  </si>
-  <si>
-    <t>YAZMIN SINAI</t>
-  </si>
-  <si>
-    <t>ZAID RAUL</t>
-  </si>
-  <si>
-    <t>MARIA DE LOS ANGELES</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>SERGIO FARITH</t>
-  </si>
-  <si>
-    <t>AGUSTIN ARTURO</t>
-  </si>
-  <si>
-    <t>ADAMARI</t>
-  </si>
-  <si>
-    <t>JULISSA</t>
-  </si>
-  <si>
-    <t>ERIK</t>
-  </si>
-  <si>
-    <t>ROSA LIZBETH</t>
   </si>
   <si>
     <t>OZIEL</t>
@@ -1158,7 +1158,7 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>6</v>
@@ -1170,13 +1170,13 @@
         <v>6</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>5</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1188,7 +1188,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1212,7 +1212,7 @@
         <v>5</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>6</v>
@@ -1224,7 +1224,7 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1309,10 +1309,10 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>9</v>
@@ -1324,13 +1324,13 @@
         <v>6</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>7</v>
@@ -1342,7 +1342,7 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1363,10 +1363,10 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1378,7 +1378,7 @@
         <v>6</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1478,7 +1478,7 @@
         <v>6</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <v>7</v>
@@ -1496,7 +1496,7 @@
         <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1532,7 +1532,7 @@
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1694,10 +1694,10 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>6</v>
@@ -1709,13 +1709,13 @@
         <v>5</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>4</v>
@@ -1727,7 +1727,7 @@
         <v>7</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1748,10 +1748,10 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -1763,7 +1763,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1925,10 +1925,10 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>4</v>
@@ -1940,13 +1940,13 @@
         <v>6</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>5</v>
@@ -1958,7 +1958,7 @@
         <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1979,10 +1979,10 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
         <v>5</v>
@@ -1994,7 +1994,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2002,10 +2002,10 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>4</v>
@@ -2017,13 +2017,13 @@
         <v>5</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -2035,7 +2035,7 @@
         <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2056,10 +2056,10 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -2071,7 +2071,7 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2236,7 +2236,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>6</v>
@@ -2254,7 +2254,7 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -2290,7 +2290,7 @@
         <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2325,7 +2325,7 @@
         <v>8</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>5</v>
@@ -2343,7 +2343,7 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2379,7 +2379,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -3326,7 +3326,7 @@
         <v>8</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H34">
         <v>5</v>
@@ -3344,7 +3344,7 @@
         <v>9</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3380,7 +3380,7 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3468,7 +3468,7 @@
         <v>5</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -3480,13 +3480,13 @@
         <v>7</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H36">
         <v>5</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J36">
         <v>4</v>
@@ -3498,7 +3498,7 @@
         <v>6</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3522,7 +3522,7 @@
         <v>5</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V36">
         <v>5</v>
@@ -3534,7 +3534,7 @@
         <v>7</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3542,7 +3542,7 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>7</v>
@@ -3560,7 +3560,7 @@
         <v>6</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>5</v>
@@ -3596,7 +3596,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U37">
         <v>6</v>
@@ -4138,30 +4138,30 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="G2">
-        <v>27.5</v>
+        <v>37.5</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -4170,30 +4170,30 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G3">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>22.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -4214,7 +4214,7 @@
         <v>20</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4237,22 +4237,22 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F5">
         <v>82.5</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>17.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4326,7 +4326,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4351,426 +4351,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920261</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920261</v>
-      </c>
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920263</v>
-      </c>
-      <c r="B4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920263</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920263</v>
-      </c>
-      <c r="B6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920402</v>
-      </c>
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920403</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920403</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920403</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920377</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920377</v>
-      </c>
-      <c r="B12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920377</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" t="s">
-        <v>93</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920410</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" t="s">
-        <v>94</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920410</v>
-      </c>
-      <c r="B15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920410</v>
-      </c>
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920405</v>
-      </c>
-      <c r="B17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920372</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D18" t="s">
-        <v>96</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920281</v>
-      </c>
-      <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" t="s">
-        <v>97</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920395</v>
-      </c>
-      <c r="B20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920395</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>87</v>
-      </c>
-      <c r="D21" t="s">
-        <v>98</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920279</v>
-      </c>
-      <c r="B22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" t="s">
-        <v>99</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -4806,104 +4386,104 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920263</v>
+        <v>22330051920261</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920403</v>
+        <v>21330051920396</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920377</v>
+        <v>22330051920260</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920410</v>
+        <v>22330051920416</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920261</v>
+        <v>22330051920263</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920395</v>
+        <v>22330051920262</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4911,95 +4491,95 @@
         <v>22330051920402</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920405</v>
+        <v>22330051920420</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920372</v>
+        <v>22330051920264</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920281</v>
+        <v>22330051920403</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920279</v>
+        <v>22330051920404</v>
       </c>
       <c r="B12" t="s">
         <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920396</v>
+        <v>22330051920377</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
         <v>140</v>
@@ -5010,10 +4590,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920260</v>
+        <v>22330051920409</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
         <v>112</v>
@@ -5027,13 +4607,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920416</v>
+        <v>22330051920410</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
         <v>142</v>
@@ -5044,13 +4624,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920262</v>
+        <v>22330051920265</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
         <v>143</v>
@@ -5061,13 +4641,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920420</v>
+        <v>22330051920411</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="D17" t="s">
         <v>144</v>
@@ -5078,13 +4658,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920264</v>
+        <v>22330051920405</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
         <v>145</v>
@@ -5095,13 +4675,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920404</v>
+        <v>22330051920372</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
         <v>146</v>
@@ -5112,13 +4692,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920409</v>
+        <v>22330051920266</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
         <v>147</v>
@@ -5129,13 +4709,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920265</v>
+        <v>22330051920268</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
         <v>148</v>
@@ -5146,13 +4726,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920411</v>
+        <v>22330051920270</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s">
         <v>149</v>
@@ -5163,13 +4743,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920266</v>
+        <v>22330051920271</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="D23" t="s">
         <v>150</v>
@@ -5180,13 +4760,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920268</v>
+        <v>22330051920272</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
         <v>151</v>
@@ -5197,13 +4777,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920270</v>
+        <v>22330051920367</v>
       </c>
       <c r="B25" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
         <v>152</v>
@@ -5214,13 +4794,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920271</v>
+        <v>22330051920274</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D26" t="s">
         <v>153</v>
@@ -5231,16 +4811,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920272</v>
+        <v>22330051920273</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -5248,16 +4828,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920367</v>
+        <v>22330051920375</v>
       </c>
       <c r="B28" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5265,16 +4845,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920274</v>
+        <v>22330051920406</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5282,16 +4862,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920273</v>
+        <v>22330051920276</v>
       </c>
       <c r="B30" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="D30" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -5299,13 +4879,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920375</v>
+        <v>22330051920281</v>
       </c>
       <c r="B31" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
         <v>157</v>
@@ -5316,16 +4896,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330051920406</v>
+        <v>22330051920277</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -5333,16 +4913,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>22330051920276</v>
+        <v>22330051920280</v>
       </c>
       <c r="B33" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -5350,16 +4930,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>22330051920277</v>
+        <v>22330051920395</v>
       </c>
       <c r="B34" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="D34" t="s">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -5367,13 +4947,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>22330051920280</v>
+        <v>22330051920279</v>
       </c>
       <c r="B35" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D35" t="s">
         <v>160</v>
@@ -5387,10 +4967,10 @@
         <v>22330051920407</v>
       </c>
       <c r="B36" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C36" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D36" t="s">
         <v>161</v>
@@ -5404,10 +4984,10 @@
         <v>22330051920282</v>
       </c>
       <c r="B37" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D37" t="s">
         <v>162</v>
@@ -5421,13 +5001,13 @@
         <v>22330051920283</v>
       </c>
       <c r="B38" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D38" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -5438,10 +5018,10 @@
         <v>22330051920285</v>
       </c>
       <c r="B39" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="D39" t="s">
         <v>163</v>
@@ -5455,10 +5035,10 @@
         <v>22330051920286</v>
       </c>
       <c r="B40" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="D40" t="s">
         <v>164</v>
@@ -5472,10 +5052,10 @@
         <v>22330051920288</v>
       </c>
       <c r="B41" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="C41" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="D41" t="s">
         <v>165</v>
@@ -5491,7 +5071,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5523,22 +5103,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920402</v>
+        <v>22330051920263</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5546,25 +5126,25 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920402</v>
+        <v>22330051920263</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -5572,13 +5152,13 @@
         <v>22330051920279</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -5595,22 +5175,22 @@
         <v>22330051920279</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -5618,13 +5198,13 @@
         <v>21330051920396</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -5638,19 +5218,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920404</v>
+        <v>22330051920402</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>62</v>
@@ -5661,22 +5241,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920265</v>
+        <v>22330051920404</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5684,16 +5264,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920411</v>
+        <v>22330051920265</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="D9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
@@ -5707,45 +5287,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920405</v>
+        <v>22330051920411</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920270</v>
+        <v>22330051920405</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5753,22 +5333,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920272</v>
+        <v>22330051920270</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5776,16 +5356,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920274</v>
+        <v>22330051920272</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
         <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
@@ -5799,16 +5379,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920406</v>
+        <v>22330051920274</v>
       </c>
       <c r="B14" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -5822,16 +5402,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920283</v>
+        <v>22330051920406</v>
       </c>
       <c r="B15" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>155</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
@@ -5845,24 +5425,47 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
+        <v>22330051920283</v>
+      </c>
+      <c r="B16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" t="s">
+        <v>129</v>
+      </c>
+      <c r="E16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
         <v>22330051920288</v>
       </c>
-      <c r="B16" t="s">
-        <v>120</v>
-      </c>
-      <c r="C16" t="s">
-        <v>139</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="B17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" t="s">
         <v>165</v>
       </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>63</v>
-      </c>
-      <c r="G16">
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DV - Estadisticos 20221.xlsx
+++ b/grupos/1DV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="166">
   <si>
     <t>Materia</t>
   </si>
@@ -215,10 +215,10 @@
     <t>Medina Tolentino Francisco</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
     <t>NC</t>
@@ -1043,10 +1043,10 @@
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -1120,10 +1120,10 @@
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1138,10 +1138,10 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1197,10 +1197,10 @@
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1218,7 +1218,7 @@
         <v>6</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -1274,10 +1274,10 @@
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1351,10 +1351,10 @@
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1372,7 +1372,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>6</v>
@@ -1428,10 +1428,10 @@
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1505,10 +1505,10 @@
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1526,7 +1526,7 @@
         <v>5</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1582,10 +1582,10 @@
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1600,10 +1600,10 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>6</v>
@@ -1659,10 +1659,10 @@
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1736,10 +1736,10 @@
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1757,7 +1757,7 @@
         <v>5</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -1813,10 +1813,10 @@
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1890,10 +1890,10 @@
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1908,7 +1908,7 @@
         <v>6</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1967,10 +1967,10 @@
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2044,10 +2044,10 @@
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2065,7 +2065,7 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -2121,10 +2121,10 @@
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2139,7 +2139,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2198,10 +2198,10 @@
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2275,10 +2275,10 @@
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2352,10 +2352,10 @@
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2373,7 +2373,7 @@
         <v>5</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2429,10 +2429,10 @@
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2506,10 +2506,10 @@
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2583,10 +2583,10 @@
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2601,7 +2601,7 @@
         <v>6</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>9</v>
@@ -2660,10 +2660,10 @@
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2737,10 +2737,10 @@
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2755,7 +2755,7 @@
         <v>6</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -2814,10 +2814,10 @@
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -2891,10 +2891,10 @@
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -2912,7 +2912,7 @@
         <v>7</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>7</v>
@@ -2968,10 +2968,10 @@
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3045,10 +3045,10 @@
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3063,10 +3063,10 @@
         <v>6</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>7</v>
@@ -3122,10 +3122,10 @@
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3140,10 +3140,10 @@
         <v>6</v>
       </c>
       <c r="V31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -3199,10 +3199,10 @@
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3276,10 +3276,10 @@
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3294,10 +3294,10 @@
         <v>6</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>7</v>
@@ -3353,10 +3353,10 @@
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3374,7 +3374,7 @@
         <v>6</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>9</v>
@@ -3430,10 +3430,10 @@
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -3507,10 +3507,10 @@
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -3528,7 +3528,7 @@
         <v>5</v>
       </c>
       <c r="W36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X36">
         <v>7</v>
@@ -3584,10 +3584,10 @@
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -3605,7 +3605,7 @@
         <v>7</v>
       </c>
       <c r="W37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X37">
         <v>5</v>
@@ -3661,10 +3661,10 @@
         <v>-1</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -3682,7 +3682,7 @@
         <v>8</v>
       </c>
       <c r="W38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X38">
         <v>7</v>
@@ -3738,10 +3738,10 @@
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -3815,10 +3815,10 @@
         <v>-1</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -3836,7 +3836,7 @@
         <v>7</v>
       </c>
       <c r="W40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>9</v>
@@ -3892,10 +3892,10 @@
         <v>-1</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R41">
         <v>-1</v>
@@ -3913,7 +3913,7 @@
         <v>8</v>
       </c>
       <c r="W41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X41">
         <v>7</v>
@@ -3969,10 +3969,10 @@
         <v>-1</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R42">
         <v>-1</v>
@@ -3987,10 +3987,10 @@
         <v>7</v>
       </c>
       <c r="V42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X42">
         <v>7</v>
@@ -4046,10 +4046,10 @@
         <v>-1</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R43">
         <v>-1</v>
@@ -4064,7 +4064,7 @@
         <v>6</v>
       </c>
       <c r="V43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W43">
         <v>9</v>
@@ -4182,7 +4182,7 @@
         <v>20</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4257,7 +4257,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
@@ -4266,19 +4266,19 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4289,7 +4289,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
@@ -4298,19 +4298,19 @@
         <v>40</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>92.5</v>
+        <v>97.5</v>
       </c>
       <c r="G7">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5071,7 +5071,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5103,16 +5103,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920263</v>
+        <v>21330051920396</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5126,22 +5126,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920263</v>
+        <v>21330051920396</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5149,16 +5149,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920279</v>
+        <v>22330051920263</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -5172,22 +5172,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920279</v>
+        <v>22330051920263</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5195,16 +5195,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920396</v>
+        <v>22330051920274</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -5218,16 +5218,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920402</v>
+        <v>22330051920274</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -5241,22 +5241,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920404</v>
+        <v>22330051920281</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D8" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5264,22 +5264,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920265</v>
+        <v>22330051920281</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5287,16 +5287,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920411</v>
+        <v>22330051920279</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D10" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -5310,22 +5310,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920405</v>
+        <v>22330051920279</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="D11" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5333,16 +5333,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920270</v>
+        <v>22330051920402</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -5356,22 +5356,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920272</v>
+        <v>22330051920404</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5379,16 +5379,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920274</v>
+        <v>22330051920265</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D14" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -5402,16 +5402,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920406</v>
+        <v>22330051920411</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
@@ -5425,22 +5425,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920283</v>
+        <v>22330051920405</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -5448,24 +5448,70 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920288</v>
+        <v>22330051920272</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920406</v>
+      </c>
+      <c r="B18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>155</v>
+      </c>
+      <c r="E18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920283</v>
+      </c>
+      <c r="B19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" t="s">
+        <v>126</v>
+      </c>
+      <c r="D19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DV - Estadisticos 20221.xlsx
+++ b/grupos/1DV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="166">
   <si>
     <t>Materia</t>
   </si>
@@ -1049,7 +1049,7 @@
         <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -1126,7 +1126,7 @@
         <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1203,7 +1203,7 @@
         <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1221,7 +1221,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>5</v>
@@ -1280,7 +1280,7 @@
         <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1357,7 +1357,7 @@
         <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1434,7 +1434,7 @@
         <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1511,7 +1511,7 @@
         <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1529,7 +1529,7 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>6</v>
@@ -1588,7 +1588,7 @@
         <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1665,7 +1665,7 @@
         <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1683,7 +1683,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1742,7 +1742,7 @@
         <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1819,7 +1819,7 @@
         <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1837,7 +1837,7 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1896,7 +1896,7 @@
         <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1914,7 +1914,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1973,7 +1973,7 @@
         <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -2050,7 +2050,7 @@
         <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2127,7 +2127,7 @@
         <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2204,7 +2204,7 @@
         <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2281,7 +2281,7 @@
         <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2358,7 +2358,7 @@
         <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2435,7 +2435,7 @@
         <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2512,7 +2512,7 @@
         <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2589,7 +2589,7 @@
         <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2666,7 +2666,7 @@
         <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2743,7 +2743,7 @@
         <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2820,7 +2820,7 @@
         <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2897,7 +2897,7 @@
         <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -2915,7 +2915,7 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -2974,7 +2974,7 @@
         <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -3051,7 +3051,7 @@
         <v>6</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3069,7 +3069,7 @@
         <v>6</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y30">
         <v>8</v>
@@ -3128,7 +3128,7 @@
         <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3205,7 +3205,7 @@
         <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3223,7 +3223,7 @@
         <v>9</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>8</v>
@@ -3282,7 +3282,7 @@
         <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3359,7 +3359,7 @@
         <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3377,7 +3377,7 @@
         <v>7</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>5</v>
@@ -3436,7 +3436,7 @@
         <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3513,7 +3513,7 @@
         <v>8</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S36">
         <v>-1</v>
@@ -3531,7 +3531,7 @@
         <v>6</v>
       </c>
       <c r="X36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>5</v>
@@ -3590,7 +3590,7 @@
         <v>9</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S37">
         <v>-1</v>
@@ -3608,7 +3608,7 @@
         <v>6</v>
       </c>
       <c r="X37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y37">
         <v>6</v>
@@ -3667,7 +3667,7 @@
         <v>9</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S38">
         <v>-1</v>
@@ -3744,7 +3744,7 @@
         <v>9</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S39">
         <v>-1</v>
@@ -3821,7 +3821,7 @@
         <v>8</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S40">
         <v>-1</v>
@@ -3839,7 +3839,7 @@
         <v>8</v>
       </c>
       <c r="X40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y40">
         <v>6</v>
@@ -3898,7 +3898,7 @@
         <v>9</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S41">
         <v>-1</v>
@@ -3975,7 +3975,7 @@
         <v>9</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S42">
         <v>-1</v>
@@ -3993,7 +3993,7 @@
         <v>9</v>
       </c>
       <c r="X42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y42">
         <v>8</v>
@@ -4052,7 +4052,7 @@
         <v>9</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S43">
         <v>-1</v>
@@ -4266,19 +4266,19 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="G6">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5071,7 +5071,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5241,16 +5241,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920281</v>
+        <v>22330051920279</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -5264,22 +5264,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920281</v>
+        <v>22330051920279</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5287,22 +5287,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920279</v>
+        <v>22330051920402</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5310,16 +5310,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920279</v>
+        <v>22330051920404</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920402</v>
+        <v>22330051920265</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5356,22 +5356,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920404</v>
+        <v>22330051920411</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5379,22 +5379,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920265</v>
+        <v>22330051920405</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5402,16 +5402,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920411</v>
+        <v>22330051920272</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D15" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
@@ -5425,22 +5425,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920405</v>
+        <v>22330051920406</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -5448,16 +5448,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920272</v>
+        <v>22330051920281</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D17" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E17" t="s">
         <v>5</v>
@@ -5471,16 +5471,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920406</v>
+        <v>22330051920283</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="D18" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
@@ -5489,29 +5489,6 @@
         <v>61</v>
       </c>
       <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920283</v>
-      </c>
-      <c r="B19" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D19" t="s">
-        <v>129</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DV - Estadisticos 20221.xlsx
+++ b/grupos/1DV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="166">
   <si>
     <t>Materia</t>
   </si>
@@ -206,13 +206,13 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Medina Tolentino Francisco</t>
+  </si>
+  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
     <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Francisco</t>
   </si>
   <si>
     <t>Pesce Bautista Victor Manuel</t>
@@ -1040,7 +1040,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>8</v>
@@ -1052,13 +1052,13 @@
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>9</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -1117,7 +1117,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>4</v>
@@ -1129,13 +1129,13 @@
         <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
         <v>5</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -1194,7 +1194,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>6</v>
@@ -1206,13 +1206,13 @@
         <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>5</v>
       </c>
       <c r="U6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>6</v>
@@ -1224,7 +1224,7 @@
         <v>6</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1271,7 +1271,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
         <v>8</v>
@@ -1283,7 +1283,7 @@
         <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -1301,7 +1301,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1348,7 +1348,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
         <v>8</v>
@@ -1360,7 +1360,7 @@
         <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>5</v>
@@ -1378,7 +1378,7 @@
         <v>6</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1425,7 +1425,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>9</v>
@@ -1437,13 +1437,13 @@
         <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>6</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1502,7 +1502,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
         <v>7</v>
@@ -1514,13 +1514,13 @@
         <v>6</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>7</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -1532,7 +1532,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1579,7 +1579,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>10</v>
@@ -1591,13 +1591,13 @@
         <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>8</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1609,7 +1609,7 @@
         <v>6</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1656,7 +1656,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
         <v>9</v>
@@ -1668,7 +1668,7 @@
         <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>6</v>
@@ -1686,7 +1686,7 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1733,7 +1733,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
         <v>6</v>
@@ -1745,7 +1745,7 @@
         <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
         <v>6</v>
@@ -1763,7 +1763,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1810,7 +1810,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
         <v>7</v>
@@ -1822,7 +1822,7 @@
         <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>6</v>
@@ -1840,7 +1840,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1887,7 +1887,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>7</v>
@@ -1899,13 +1899,13 @@
         <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>7</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -1917,7 +1917,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1964,7 +1964,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
         <v>4</v>
@@ -1976,7 +1976,7 @@
         <v>5</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>5</v>
@@ -2041,7 +2041,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>4</v>
@@ -2053,7 +2053,7 @@
         <v>5</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>5</v>
@@ -2118,7 +2118,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>9</v>
@@ -2130,13 +2130,13 @@
         <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>5</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2195,7 +2195,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>7</v>
@@ -2207,7 +2207,7 @@
         <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>5</v>
@@ -2225,7 +2225,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2272,7 +2272,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
         <v>7</v>
@@ -2284,7 +2284,7 @@
         <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>6</v>
@@ -2349,7 +2349,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>7</v>
@@ -2361,13 +2361,13 @@
         <v>6</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
         <v>5</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -2426,7 +2426,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>8</v>
@@ -2438,13 +2438,13 @@
         <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>9</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -2503,7 +2503,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
         <v>7</v>
@@ -2515,13 +2515,13 @@
         <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>7</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -2580,7 +2580,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
         <v>8</v>
@@ -2592,13 +2592,13 @@
         <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>6</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>6</v>
@@ -2657,7 +2657,7 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
         <v>7</v>
@@ -2669,7 +2669,7 @@
         <v>7</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
         <v>6</v>
@@ -2734,7 +2734,7 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>6</v>
@@ -2746,13 +2746,13 @@
         <v>7</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>5</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>6</v>
@@ -2811,7 +2811,7 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
         <v>7</v>
@@ -2823,7 +2823,7 @@
         <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
         <v>7</v>
@@ -2841,7 +2841,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2888,7 +2888,7 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
         <v>7</v>
@@ -2900,7 +2900,7 @@
         <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
         <v>7</v>
@@ -2965,7 +2965,7 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
         <v>7</v>
@@ -2977,7 +2977,7 @@
         <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T29">
         <v>7</v>
@@ -3042,7 +3042,7 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
         <v>4</v>
@@ -3054,13 +3054,13 @@
         <v>5</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
         <v>5</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V30">
         <v>5</v>
@@ -3072,7 +3072,7 @@
         <v>6</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3119,7 +3119,7 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
         <v>6</v>
@@ -3131,7 +3131,7 @@
         <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>5</v>
@@ -3196,7 +3196,7 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
         <v>10</v>
@@ -3208,13 +3208,13 @@
         <v>8</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>8</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V32">
         <v>8</v>
@@ -3226,7 +3226,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
         <v>6</v>
@@ -3285,7 +3285,7 @@
         <v>6</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T33">
         <v>6</v>
@@ -3350,7 +3350,7 @@
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
         <v>7</v>
@@ -3362,13 +3362,13 @@
         <v>7</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
         <v>5</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>6</v>
@@ -3380,7 +3380,7 @@
         <v>8</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3427,7 +3427,7 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P35">
         <v>6</v>
@@ -3439,7 +3439,7 @@
         <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
         <v>6</v>
@@ -3504,7 +3504,7 @@
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P36">
         <v>5</v>
@@ -3516,7 +3516,7 @@
         <v>6</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T36">
         <v>5</v>
@@ -3534,7 +3534,7 @@
         <v>6</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3581,7 +3581,7 @@
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
         <v>7</v>
@@ -3593,13 +3593,13 @@
         <v>7</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T37">
         <v>5</v>
       </c>
       <c r="U37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V37">
         <v>7</v>
@@ -3611,7 +3611,7 @@
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3658,7 +3658,7 @@
         <v>-1</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P38">
         <v>8</v>
@@ -3670,13 +3670,13 @@
         <v>7</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T38">
         <v>6</v>
       </c>
       <c r="U38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V38">
         <v>8</v>
@@ -3735,7 +3735,7 @@
         <v>-1</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P39">
         <v>8</v>
@@ -3747,13 +3747,13 @@
         <v>8</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T39">
         <v>6</v>
       </c>
       <c r="U39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V39">
         <v>7</v>
@@ -3812,7 +3812,7 @@
         <v>-1</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P40">
         <v>8</v>
@@ -3824,7 +3824,7 @@
         <v>7</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T40">
         <v>5</v>
@@ -3889,7 +3889,7 @@
         <v>-1</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P41">
         <v>9</v>
@@ -3901,7 +3901,7 @@
         <v>7</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T41">
         <v>7</v>
@@ -3919,7 +3919,7 @@
         <v>7</v>
       </c>
       <c r="Y41">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3966,7 +3966,7 @@
         <v>-1</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P42">
         <v>9</v>
@@ -3978,7 +3978,7 @@
         <v>6</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T42">
         <v>6</v>
@@ -4043,7 +4043,7 @@
         <v>-1</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P43">
         <v>9</v>
@@ -4055,7 +4055,7 @@
         <v>7</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T43">
         <v>7</v>
@@ -4073,7 +4073,7 @@
         <v>7</v>
       </c>
       <c r="Y43">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4161,7 +4161,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -4170,19 +4170,19 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4193,7 +4193,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -4225,7 +4225,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
@@ -4234,19 +4234,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>82.5</v>
+        <v>90</v>
       </c>
       <c r="G5">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5071,7 +5071,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5141,7 +5141,7 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5187,7 +5187,7 @@
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5195,22 +5195,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920274</v>
+        <v>22330051920402</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5218,22 +5218,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920274</v>
+        <v>22330051920402</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5241,22 +5241,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920279</v>
+        <v>22330051920403</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="D8" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5264,19 +5264,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920279</v>
+        <v>22330051920403</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
         <v>63</v>
@@ -5287,22 +5287,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920402</v>
+        <v>22330051920261</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5310,22 +5310,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920404</v>
+        <v>22330051920265</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5333,16 +5333,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920265</v>
+        <v>22330051920411</v>
       </c>
       <c r="B12" t="s">
         <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -5356,22 +5356,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920411</v>
+        <v>22330051920405</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5379,22 +5379,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920405</v>
+        <v>22330051920272</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="D14" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5402,16 +5402,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920272</v>
+        <v>22330051920406</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
@@ -5425,16 +5425,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920406</v>
+        <v>22330051920279</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="D16" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -5448,16 +5448,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920281</v>
+        <v>22330051920283</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D17" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="E17" t="s">
         <v>5</v>
@@ -5466,29 +5466,6 @@
         <v>61</v>
       </c>
       <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920283</v>
-      </c>
-      <c r="B18" t="s">
-        <v>100</v>
-      </c>
-      <c r="C18" t="s">
-        <v>126</v>
-      </c>
-      <c r="D18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DV - Estadisticos 20221.xlsx
+++ b/grupos/1DV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="166">
   <si>
     <t>Materia</t>
   </si>
@@ -203,13 +203,13 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Medina Tolentino Francisco</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Francisco</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
     <t>Velasco Sánchez David</t>
@@ -1037,7 +1037,7 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>10</v>
@@ -1114,7 +1114,7 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
         <v>5</v>
@@ -1132,7 +1132,7 @@
         <v>6</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U5">
         <v>6</v>
@@ -1191,7 +1191,7 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>8</v>
@@ -1209,7 +1209,7 @@
         <v>7</v>
       </c>
       <c r="T6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U6">
         <v>6</v>
@@ -1268,7 +1268,7 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>8</v>
@@ -1345,7 +1345,7 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
         <v>5</v>
@@ -1363,7 +1363,7 @@
         <v>8</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U8">
         <v>5</v>
@@ -1422,7 +1422,7 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
         <v>9</v>
@@ -1499,7 +1499,7 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>5</v>
@@ -1517,7 +1517,7 @@
         <v>8</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1576,7 +1576,7 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -1653,7 +1653,7 @@
         <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
         <v>7</v>
@@ -1671,7 +1671,7 @@
         <v>9</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>7</v>
@@ -1730,7 +1730,7 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
         <v>5</v>
@@ -1807,7 +1807,7 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>9</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>7</v>
@@ -1884,7 +1884,7 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
         <v>8</v>
@@ -1961,7 +1961,7 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>5</v>
@@ -2038,7 +2038,7 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>5</v>
@@ -2115,7 +2115,7 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>8</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>9</v>
@@ -2192,7 +2192,7 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>7</v>
@@ -2210,7 +2210,7 @@
         <v>6</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2269,7 +2269,7 @@
         <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
         <v>5</v>
@@ -2346,7 +2346,7 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>5</v>
@@ -2423,7 +2423,7 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
         <v>10</v>
@@ -2500,7 +2500,7 @@
         <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>5</v>
@@ -2577,7 +2577,7 @@
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
         <v>8</v>
@@ -2595,7 +2595,7 @@
         <v>7</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>7</v>
@@ -2654,7 +2654,7 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -2731,7 +2731,7 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
         <v>10</v>
@@ -2749,7 +2749,7 @@
         <v>7</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U26">
         <v>7</v>
@@ -2808,7 +2808,7 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
         <v>7</v>
@@ -2826,7 +2826,7 @@
         <v>6</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>6</v>
@@ -2885,7 +2885,7 @@
         <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
         <v>7</v>
@@ -2962,7 +2962,7 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <v>7</v>
@@ -2980,7 +2980,7 @@
         <v>7</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U29">
         <v>7</v>
@@ -3039,7 +3039,7 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O30">
         <v>5</v>
@@ -3116,7 +3116,7 @@
         <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>7</v>
@@ -3134,7 +3134,7 @@
         <v>7</v>
       </c>
       <c r="T31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U31">
         <v>6</v>
@@ -3193,7 +3193,7 @@
         <v>7</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
         <v>6</v>
@@ -3270,7 +3270,7 @@
         <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
         <v>7</v>
@@ -3288,7 +3288,7 @@
         <v>7</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>6</v>
@@ -3347,7 +3347,7 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
         <v>9</v>
@@ -3365,7 +3365,7 @@
         <v>7</v>
       </c>
       <c r="T34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U34">
         <v>8</v>
@@ -3424,7 +3424,7 @@
         <v>7</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O35">
         <v>7</v>
@@ -3501,7 +3501,7 @@
         <v>6</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O36">
         <v>5</v>
@@ -3519,7 +3519,7 @@
         <v>7</v>
       </c>
       <c r="T36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U36">
         <v>5</v>
@@ -3578,7 +3578,7 @@
         <v>6</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O37">
         <v>5</v>
@@ -3596,7 +3596,7 @@
         <v>5</v>
       </c>
       <c r="T37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U37">
         <v>5</v>
@@ -3655,7 +3655,7 @@
         <v>5</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O38">
         <v>8</v>
@@ -3732,7 +3732,7 @@
         <v>7</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O39">
         <v>8</v>
@@ -3750,7 +3750,7 @@
         <v>8</v>
       </c>
       <c r="T39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U39">
         <v>7</v>
@@ -3809,7 +3809,7 @@
         <v>6</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O40">
         <v>6</v>
@@ -3827,7 +3827,7 @@
         <v>7</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U40">
         <v>6</v>
@@ -3886,7 +3886,7 @@
         <v>6</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O41">
         <v>6</v>
@@ -3963,7 +3963,7 @@
         <v>8</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O42">
         <v>7</v>
@@ -4040,7 +4040,7 @@
         <v>9</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O43">
         <v>7</v>
@@ -4058,7 +4058,7 @@
         <v>6</v>
       </c>
       <c r="T43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U43">
         <v>6</v>
@@ -4129,7 +4129,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
@@ -4138,19 +4138,19 @@
         <v>40</v>
       </c>
       <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>75</v>
+      </c>
+      <c r="G2">
         <v>25</v>
       </c>
-      <c r="E2">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>62.5</v>
-      </c>
-      <c r="G2">
-        <v>37.5</v>
-      </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4161,7 +4161,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -4170,19 +4170,19 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4193,7 +4193,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -4202,19 +4202,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5071,7 +5071,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5103,19 +5103,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920396</v>
+        <v>22330051920402</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>61</v>
@@ -5126,22 +5126,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920396</v>
+        <v>22330051920402</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5149,19 +5149,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920263</v>
+        <v>22330051920403</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>61</v>
@@ -5172,19 +5172,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920263</v>
+        <v>22330051920403</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>62</v>
@@ -5195,22 +5195,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920402</v>
+        <v>22330051920281</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5218,22 +5218,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920402</v>
+        <v>22330051920281</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5241,22 +5241,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920403</v>
+        <v>22330051920395</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="D8" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5264,22 +5264,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920403</v>
+        <v>22330051920395</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5287,22 +5287,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920261</v>
+        <v>21330051920396</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5310,19 +5310,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920265</v>
+        <v>22330051920263</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>61</v>
@@ -5333,139 +5333,24 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920411</v>
+        <v>22330051920405</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>61</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920405</v>
-      </c>
-      <c r="B13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" t="s">
-        <v>145</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920272</v>
-      </c>
-      <c r="B14" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920406</v>
-      </c>
-      <c r="B15" t="s">
-        <v>92</v>
-      </c>
-      <c r="C15" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" t="s">
-        <v>155</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920279</v>
-      </c>
-      <c r="B16" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" t="s">
-        <v>123</v>
-      </c>
-      <c r="D16" t="s">
-        <v>160</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920283</v>
-      </c>
-      <c r="B17" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" t="s">
-        <v>126</v>
-      </c>
-      <c r="D17" t="s">
-        <v>129</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17">
         <v>5</v>
       </c>
     </row>
